--- a/data/deepdive/台股深度_2330.xlsx
+++ b/data/deepdive/台股深度_2330.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,7 +587,9 @@
           <t>月營收 YoY%</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>30.1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -710,7 +712,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>─── 事件雷達 ───</t>
+          <t>─── 3:1 混合版 (推薦) ───</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -718,156 +720,260 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>外資 5d 淨(千股)</t>
+          <t>混合 SL 技術 (近 3M 低×1.03)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-16323</v>
+        <v>1854.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>外資 20d 淨(千股)</t>
+          <t>混合 SL 基本面 (EPS×15x)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-119327</v>
+        <v>1115.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>外資 5d↔20d</t>
+          <t>混合 SL 採用</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>同向</t>
+          <t>1854.2 (技術)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>外資持股 5d 變化 (pp)</t>
+          <t>混合 TP 技術 (52w 高×1.05)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.08</v>
+        <v>2661.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>─── 籌碼 90d ───</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>混合 TP 基本面 (EPS×26x)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1934.14</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>外資淨(千股)</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>-211199</v>
+          <t>混合 TP 採用</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1934.14 (基本面)</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>投信淨(千股)</t>
+          <t>混合 Max Entry</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63166</v>
+        <v>1874.19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>自營淨(千股)</t>
+          <t>混合 距 Max Entry %</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13334</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>三大合計(千股)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>-134699</v>
+          <t>混合 判讀</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>🔴 追高風險(&gt;15%)</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>外資持股%</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>69.77</v>
-      </c>
+          <t>─── 事件雷達 ───</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>─── 散戶 ───</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>外資 5d 淨(千股)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-16323</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>融資餘額(張)</t>
+          <t>外資 20d 淨(千股)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32</v>
+        <v>-119327</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>融券餘額(張)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
+          <t>外資 5d↔20d</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>同向</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>─── 警戒 ───</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>外資持股 5d 變化 (pp)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.08</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1y 處置</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+          <t>─── 籌碼 90d ───</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>外資淨(千股)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>-211199</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>投信淨(千股)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>63166</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>自營淨(千股)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>13334</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>三大合計(千股)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>-134699</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>外資持股%</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>69.77</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>─── 散戶 ───</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>融資餘額(張)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>融券餘額(張)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>─── 警戒 ───</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1y 處置</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>1y 暫停</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67790,7 +67896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67804,6 +67910,16 @@
           <t>營收(億)</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>YoY%</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MoM%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -67814,6 +67930,12 @@
       <c r="B2" t="n">
         <v>4169.75</v>
       </c>
+      <c r="C2" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -67824,6 +67946,12 @@
       <c r="B3" t="n">
         <v>4107.25</v>
       </c>
+      <c r="C3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -67834,6 +67962,12 @@
       <c r="B4" t="n">
         <v>4151.92</v>
       </c>
+      <c r="C4" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -67844,6 +67978,12 @@
       <c r="B5" t="n">
         <v>3176.57</v>
       </c>
+      <c r="C5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-20.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -67854,6 +67994,12 @@
       <c r="B6" t="n">
         <v>4012.55</v>
       </c>
+      <c r="C6" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -67864,6 +68010,12 @@
       <c r="B7" t="n">
         <v>3350.04</v>
       </c>
+      <c r="C7" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -67874,6 +68026,12 @@
       <c r="B8" t="n">
         <v>3436.14</v>
       </c>
+      <c r="C8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-6.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -67884,6 +68042,12 @@
       <c r="B9" t="n">
         <v>3674.73</v>
       </c>
+      <c r="C9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -67894,6 +68058,12 @@
       <c r="B10" t="n">
         <v>3309.81</v>
       </c>
+      <c r="C10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -67904,6 +68074,12 @@
       <c r="B11" t="n">
         <v>3357.72</v>
       </c>
+      <c r="C11" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -67914,6 +68090,12 @@
       <c r="B12" t="n">
         <v>3231.66</v>
       </c>
+      <c r="C12" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -67924,6 +68106,12 @@
       <c r="B13" t="n">
         <v>2637.09</v>
       </c>
+      <c r="C13" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-17.7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -67934,6 +68122,12 @@
       <c r="B14" t="n">
         <v>3205.16</v>
       </c>
+      <c r="C14" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-8.300000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -67944,6 +68138,12 @@
       <c r="B15" t="n">
         <v>3495.67</v>
       </c>
+      <c r="C15" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -67954,6 +68154,12 @@
       <c r="B16" t="n">
         <v>2859.57</v>
       </c>
+      <c r="C16" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -67964,6 +68170,12 @@
       <c r="B17" t="n">
         <v>2600.09</v>
       </c>
+      <c r="C17" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-11.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -67974,6 +68186,12 @@
       <c r="B18" t="n">
         <v>2932.88</v>
       </c>
+      <c r="C18" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -67984,6 +68202,12 @@
       <c r="B19" t="n">
         <v>2781.63</v>
       </c>
+      <c r="C19" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -67994,6 +68218,12 @@
       <c r="B20" t="n">
         <v>2760.58</v>
       </c>
+      <c r="C20" t="n">
+        <v>34</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-12.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -68004,6 +68234,12 @@
       <c r="B21" t="n">
         <v>3142.4</v>
       </c>
+      <c r="C21" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24.8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -68014,6 +68250,12 @@
       <c r="B22" t="n">
         <v>2518.73</v>
       </c>
+      <c r="C22" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -68024,6 +68266,12 @@
       <c r="B23" t="n">
         <v>2508.66</v>
       </c>
+      <c r="C23" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -68034,6 +68282,12 @@
       <c r="B24" t="n">
         <v>2569.53</v>
       </c>
+      <c r="C24" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>23.6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -68044,6 +68298,12 @@
       <c r="B25" t="n">
         <v>2078.69</v>
       </c>
+      <c r="C25" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-9.5</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -68054,6 +68314,12 @@
       <c r="B26" t="n">
         <v>2296.2</v>
       </c>
+      <c r="C26" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -68064,6 +68330,12 @@
       <c r="B27" t="n">
         <v>2360.21</v>
       </c>
+      <c r="C27" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -68074,6 +68346,12 @@
       <c r="B28" t="n">
         <v>1952.11</v>
       </c>
+      <c r="C28" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -68084,6 +68362,12 @@
       <c r="B29" t="n">
         <v>1816.48</v>
       </c>
+      <c r="C29" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-15.8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -68094,6 +68378,12 @@
       <c r="B30" t="n">
         <v>2157.85</v>
       </c>
+      <c r="C30" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -68104,6 +68394,12 @@
       <c r="B31" t="n">
         <v>1763</v>
       </c>
+      <c r="C31" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-14.4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -68114,6 +68410,12 @@
       <c r="B32" t="n">
         <v>2060.26</v>
       </c>
+      <c r="C32" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-15.3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -68124,6 +68426,12 @@
       <c r="B33" t="n">
         <v>2432.03</v>
       </c>
+      <c r="C33" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>34.8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -68134,6 +68442,12 @@
       <c r="B34" t="n">
         <v>1804.3</v>
       </c>
+      <c r="C34" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-4.4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -68144,6 +68458,12 @@
       <c r="B35" t="n">
         <v>1886.86</v>
       </c>
+      <c r="C35" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -68154,6 +68474,12 @@
       <c r="B36" t="n">
         <v>1776.16</v>
       </c>
+      <c r="C36" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>13.6</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -68164,6 +68490,12 @@
       <c r="B37" t="n">
         <v>1564.04</v>
       </c>
+      <c r="C37" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-11.4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -68174,6 +68506,12 @@
       <c r="B38" t="n">
         <v>1765.37</v>
       </c>
+      <c r="C38" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -68184,6 +68522,12 @@
       <c r="B39" t="n">
         <v>1479</v>
       </c>
+      <c r="C39" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -68194,6 +68538,12 @@
       <c r="B40" t="n">
         <v>1454.08</v>
       </c>
+      <c r="C40" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-10.9</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -68204,6 +68554,12 @@
       <c r="B41" t="n">
         <v>1631.74</v>
       </c>
+      <c r="C41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-18.4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -68214,6 +68570,12 @@
       <c r="B42" t="n">
         <v>2000.51</v>
       </c>
+      <c r="C42" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -68224,6 +68586,12 @@
       <c r="B43" t="n">
         <v>1925.6</v>
       </c>
+      <c r="C43" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-13.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -68234,6 +68602,12 @@
       <c r="B44" t="n">
         <v>2227.06</v>
       </c>
+      <c r="C44" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -68244,6 +68618,12 @@
       <c r="B45" t="n">
         <v>2102.66</v>
       </c>
+      <c r="C45" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -68254,6 +68634,12 @@
       <c r="B46" t="n">
         <v>2082.48</v>
       </c>
+      <c r="C46" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-4.5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -68264,6 +68650,12 @@
       <c r="B47" t="n">
         <v>2181.32</v>
       </c>
+      <c r="C47" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.8</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -68274,6 +68666,12 @@
       <c r="B48" t="n">
         <v>1867.63</v>
       </c>
+      <c r="C48" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -68284,6 +68682,12 @@
       <c r="B49" t="n">
         <v>1758.74</v>
       </c>
+      <c r="C49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-5.3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -68294,6 +68698,12 @@
       <c r="B50" t="n">
         <v>1857.05</v>
       </c>
+      <c r="C50" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -68304,6 +68714,12 @@
       <c r="B51" t="n">
         <v>1725.61</v>
       </c>
+      <c r="C51" t="n">
+        <v>55</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -68314,6 +68730,12 @@
       <c r="B52" t="n">
         <v>1719.67</v>
       </c>
+      <c r="C52" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -68324,6 +68746,12 @@
       <c r="B53" t="n">
         <v>1469.33</v>
       </c>
+      <c r="C53" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-14.7</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -68334,6 +68762,12 @@
       <c r="B54" t="n">
         <v>1721.76</v>
       </c>
+      <c r="C54" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -68344,6 +68778,12 @@
       <c r="B55" t="n">
         <v>1553.82</v>
       </c>
+      <c r="C55" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -68354,6 +68794,12 @@
       <c r="B56" t="n">
         <v>1482.68</v>
       </c>
+      <c r="C56" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -68364,6 +68810,12 @@
       <c r="B57" t="n">
         <v>1345.39</v>
       </c>
+      <c r="C57" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-11.9</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -68374,6 +68826,12 @@
       <c r="B58" t="n">
         <v>1526.85</v>
       </c>
+      <c r="C58" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -68384,6 +68842,12 @@
       <c r="B59" t="n">
         <v>1374.27</v>
       </c>
+      <c r="C59" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -68394,6 +68858,12 @@
       <c r="B60" t="n">
         <v>1245.58</v>
       </c>
+      <c r="C60" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-16.1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -68404,6 +68874,12 @@
       <c r="B61" t="n">
         <v>1484.71</v>
       </c>
+      <c r="C61" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D61" t="n">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -68414,6 +68890,12 @@
       <c r="B62" t="n">
         <v>1123.6</v>
       </c>
+      <c r="C62" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -68424,6 +68906,12 @@
       <c r="B63" t="n">
         <v>1113.15</v>
       </c>
+      <c r="C63" t="n">
+        <v>16</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-13.8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -68434,6 +68922,12 @@
       <c r="B64" t="n">
         <v>1291.27</v>
       </c>
+      <c r="C64" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>21.2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -68444,6 +68938,12 @@
       <c r="B65" t="n">
         <v>1065.34</v>
       </c>
+      <c r="C65" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-15.9</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -68454,6 +68954,12 @@
       <c r="B66" t="n">
         <v>1267.49</v>
       </c>
+      <c r="C66" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -68464,6 +68970,12 @@
       <c r="B67" t="n">
         <v>1173.65</v>
       </c>
+      <c r="C67" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -68474,6 +68986,12 @@
       <c r="B68" t="n">
         <v>1248.65</v>
       </c>
+      <c r="C68" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -68484,6 +69002,12 @@
       <c r="B69" t="n">
         <v>1193.03</v>
       </c>
+      <c r="C69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-6.5</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -68494,6 +69018,12 @@
       <c r="B70" t="n">
         <v>1275.84</v>
       </c>
+      <c r="C70" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -68504,6 +69034,12 @@
       <c r="B71" t="n">
         <v>1228.78</v>
       </c>
+      <c r="C71" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -68514,6 +69050,12 @@
       <c r="B72" t="n">
         <v>1059.63</v>
       </c>
+      <c r="C72" t="n">
+        <v>25</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-12.3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -68524,6 +69066,12 @@
       <c r="B73" t="n">
         <v>1208.78</v>
       </c>
+      <c r="C73" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D73" t="n">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -68534,6 +69082,12 @@
       <c r="B74" t="n">
         <v>938.1900000000001</v>
       </c>
+      <c r="C74" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-2.3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -68544,6 +69098,12 @@
       <c r="B75" t="n">
         <v>960.02</v>
       </c>
+      <c r="C75" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-15.4</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -68554,6 +69114,12 @@
       <c r="B76" t="n">
         <v>1135.2</v>
       </c>
+      <c r="C76" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="D76" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -68564,6 +69130,12 @@
       <c r="B77" t="n">
         <v>933.9400000000001</v>
       </c>
+      <c r="C77" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-9.9</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -68574,6 +69146,12 @@
       <c r="B78" t="n">
         <v>1036.83</v>
       </c>
+      <c r="C78" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -68584,6 +69162,12 @@
       <c r="B79" t="n">
         <v>1033.13</v>
       </c>
+      <c r="C79" t="n">
+        <v>15</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-4.2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -68594,6 +69178,12 @@
       <c r="B80" t="n">
         <v>1078.84</v>
       </c>
+      <c r="C80" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -68604,6 +69194,12 @@
       <c r="B81" t="n">
         <v>1060.4</v>
       </c>
+      <c r="C81" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -68614,6 +69210,12 @@
       <c r="B82" t="n">
         <v>1021.7</v>
       </c>
+      <c r="C82" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-3.7</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -68624,6 +69226,12 @@
       <c r="B83" t="n">
         <v>1061.18</v>
       </c>
+      <c r="C83" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D83" t="n">
+        <v>25.2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -68634,6 +69242,12 @@
       <c r="B84" t="n">
         <v>847.58</v>
       </c>
+      <c r="C84" t="n">
+        <v>14</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-1.3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -68644,6 +69258,12 @@
       <c r="B85" t="n">
         <v>858.6799999999999</v>
       </c>
+      <c r="C85" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D85" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -68654,6 +69274,12 @@
       <c r="B86" t="n">
         <v>804.37</v>
       </c>
+      <c r="C86" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D86" t="n">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -68664,6 +69290,12 @@
       <c r="B87" t="n">
         <v>746.9400000000001</v>
       </c>
+      <c r="C87" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-6.3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -68674,6 +69306,12 @@
       <c r="B88" t="n">
         <v>797.22</v>
       </c>
+      <c r="C88" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>30.9</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -68684,6 +69322,12 @@
       <c r="B89" t="n">
         <v>608.89</v>
       </c>
+      <c r="C89" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -68694,6 +69338,12 @@
       <c r="B90" t="n">
         <v>780.9400000000001</v>
       </c>
+      <c r="C90" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-13.1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -68704,6 +69354,12 @@
       <c r="B91" t="n">
         <v>898.3099999999999</v>
       </c>
+      <c r="C91" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-8.699999999999999</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -68714,6 +69370,12 @@
       <c r="B92" t="n">
         <v>983.89</v>
       </c>
+      <c r="C92" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-3.1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -68724,6 +69386,12 @@
       <c r="B93" t="n">
         <v>1015.5</v>
       </c>
+      <c r="C93" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D93" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -68734,6 +69402,12 @@
       <c r="B94" t="n">
         <v>949.22</v>
       </c>
+      <c r="C94" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -68744,6 +69418,12 @@
       <c r="B95" t="n">
         <v>910.55</v>
       </c>
+      <c r="C95" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="D95" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -68754,6 +69434,12 @@
       <c r="B96" t="n">
         <v>743.71</v>
       </c>
+      <c r="C96" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -68764,6 +69450,12 @@
       <c r="B97" t="n">
         <v>704.38</v>
       </c>
+      <c r="C97" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -68774,6 +69466,12 @@
       <c r="B98" t="n">
         <v>809.6900000000001</v>
       </c>
+      <c r="C98" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -68784,6 +69482,12 @@
       <c r="B99" t="n">
         <v>818.7</v>
       </c>
+      <c r="C99" t="n">
+        <v>44</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -68794,6 +69498,12 @@
       <c r="B100" t="n">
         <v>1036.97</v>
       </c>
+      <c r="C100" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>60.4</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -68804,6 +69514,12 @@
       <c r="B101" t="n">
         <v>646.41</v>
       </c>
+      <c r="C101" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-18.9</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -68814,6 +69530,12 @@
       <c r="B102" t="n">
         <v>797.41</v>
       </c>
+      <c r="C102" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-11.3</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -68824,6 +69546,12 @@
       <c r="B103" t="n">
         <v>898.97</v>
       </c>
+      <c r="C103" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -68834,6 +69562,12 @@
       <c r="B104" t="n">
         <v>931.53</v>
       </c>
+      <c r="C104" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-1.4</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -68844,6 +69578,12 @@
       <c r="B105" t="n">
         <v>945.2</v>
       </c>
+      <c r="C105" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D105" t="n">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -68854,6 +69594,12 @@
       <c r="B106" t="n">
         <v>885.79</v>
       </c>
+      <c r="C106" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-3.6</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -68864,6 +69610,12 @@
       <c r="B107" t="n">
         <v>919.17</v>
       </c>
+      <c r="C107" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="D107" t="n">
+        <v>28.4</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -68874,6 +69626,12 @@
       <c r="B108" t="n">
         <v>716.11</v>
       </c>
+      <c r="C108" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-14.9</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -68884,6 +69642,10 @@
       <c r="B109" t="n">
         <v>841.87</v>
       </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="n">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -68894,6 +69656,10 @@
       <c r="B110" t="n">
         <v>727.96</v>
       </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -68904,6 +69670,10 @@
       <c r="B111" t="n">
         <v>568.72</v>
       </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>-33.8</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -68914,6 +69684,10 @@
       <c r="B112" t="n">
         <v>858.75</v>
       </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -68924,6 +69698,10 @@
       <c r="B113" t="n">
         <v>714.23</v>
       </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="n">
+        <v>-6.8</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -68934,6 +69712,10 @@
       <c r="B114" t="n">
         <v>766.16</v>
       </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>-1.9</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -68944,6 +69726,10 @@
       <c r="B115" t="n">
         <v>781.12</v>
       </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -68954,6 +69740,10 @@
       <c r="B116" t="n">
         <v>930.3</v>
       </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -68964,6 +69754,10 @@
       <c r="B117" t="n">
         <v>910.85</v>
       </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -68974,6 +69768,10 @@
       <c r="B118" t="n">
         <v>897.03</v>
       </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="n">
+        <v>-4.9</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -68984,6 +69782,10 @@
       <c r="B119" t="n">
         <v>943.11</v>
       </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="n">
+        <v>23.5</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -68994,6 +69796,8 @@
       <c r="B120" t="n">
         <v>763.92</v>
       </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
